--- a/job_application_forms/043_nursing_home_care_giver_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/043_nursing_home_care_giver_job_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'address',_'label':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'address', 'label': 'Address'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'fax',_'label':_'fax'}</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'fax', 'label': 'Fax'}</t>
+          <t>Fax</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'associate',_'label':_'associate'}</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'associate', 'label': 'Associate'}</t>
+          <t>Associate</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'bachelor',_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'bachelor', 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'master',_'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'master', 'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'doctorate',_'label':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'doctorate', 'label': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'morning',_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'morning', 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon',_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'afternoon', 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'evening',_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'evening', 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'night',_'label':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'night', 'label': 'Night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'nursing_home_caregiver',_'label':_'nursing_home_caregiver'}</t>
+          <t>nursing_home_caregiver</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'nursing_home_caregiver', 'label': 'Nursing Home Caregiver'}</t>
+          <t>Nursing Home Caregiver</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'caregiver',_'label':_'caregiver'}</t>
+          <t>caregiver</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'caregiver', 'label': 'Caregiver'}</t>
+          <t>Caregiver</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'healthcare_assistant',_'label':_'healthcare_assistant'}</t>
+          <t>healthcare_assistant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'healthcare_assistant', 'label': 'Healthcare Assistant'}</t>
+          <t>Healthcare Assistant</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'nurse_aide',_'label':_'nurse_aide'}</t>
+          <t>nurse_aide</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'nurse_aide', 'label': 'Nurse Aide'}</t>
+          <t>Nurse Aide</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'full_time',_'label':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'full_time', 'label': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'part_time',_'label':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'part_time', 'label': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'contract',_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'contract', 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'single',_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'single', 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'married',_'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'married', 'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'in_a_relationship',_'label':_'in_a_relationship'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'in_a_relationship', 'label': 'In a Relationship'}</t>
+          <t>In a Relationship</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
